--- a/branches/master/observations-summary.xlsx
+++ b/branches/master/observations-summary.xlsx
@@ -53,7 +53,7 @@
     <t>MII PR Labor Laboruntersuchung</t>
   </si>
   <si>
-    <t>null#26436-6, null#laboratory</t>
+    <t>null#26436-6, null#26436-6, null#laboratory</t>
   </si>
   <si>
     <t/>

--- a/branches/master/observations-summary.xlsx
+++ b/branches/master/observations-summary.xlsx
@@ -53,7 +53,7 @@
     <t>MII PR Labor Laboruntersuchung</t>
   </si>
   <si>
-    <t>null#26436-6, null#26436-6, null#laboratory</t>
+    <t>null#26436-6, null#laboratory</t>
   </si>
   <si>
     <t/>

--- a/branches/master/observations-summary.xlsx
+++ b/branches/master/observations-summary.xlsx
@@ -53,7 +53,7 @@
     <t>MII PR Labor Laboruntersuchung</t>
   </si>
   <si>
-    <t>null#26436-6, null#laboratory</t>
+    <t>null#laboratory</t>
   </si>
   <si>
     <t/>
